--- a/outputs/daily/hr_rankings_2026-06-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-11.xlsx
@@ -3535,47 +3535,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>65.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.3</v>
+        <v>53.3</v>
       </c>
       <c r="R12" t="n">
-        <v>68.3</v>
+        <v>57.2</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>54.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3669,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,112 +3699,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>102.3127</t>
+          <t>101.9188</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.5369</t>
+          <t>0.4577</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2716</t>
+          <t>0.2322</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3456</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2431</t>
+          <t>0.2351</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3815,47 +3815,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,26 +3878,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.2</v>
+        <v>65.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="R13" t="n">
-        <v>57.2</v>
+        <v>68.3</v>
       </c>
       <c r="S13" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3949,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,112 +3979,112 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.9188</t>
+          <t>102.3127</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4577</t>
+          <t>0.5369</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2322</t>
+          <t>0.2716</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3456</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.2351</t>
+          <t>0.2431</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -5495,47 +5495,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5562,22 +5562,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>49.4</v>
+        <v>53.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.3</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S19" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>53.9</v>
+        <v>28.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -5669,92 +5669,92 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.0569</t>
+          <t>102.7456</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4887</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2126</t>
+          <t>0.1927</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3675</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5775,47 +5775,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5842,22 +5842,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>36.3</v>
       </c>
       <c r="R20" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S20" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>23.4</v>
+        <v>53.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -5949,92 +5949,92 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7456</t>
+          <t>101.0569</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4887</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1927</t>
+          <t>0.2126</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7455,47 +7455,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>666397</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Edouard Julien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,26 +7518,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>51.2</v>
+        <v>39.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>55.7</v>
       </c>
       <c r="R26" t="n">
-        <v>74.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="S26" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T26" t="n">
         <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7604,127 +7604,127 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/16, 0 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>103.4467</t>
+          <t>100.1892</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4604</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2064</t>
+          <t>0.1666</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3351</t>
+          <t>0.3374</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>53.08</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1979</t>
+          <t>0.0886</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3632</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7735,47 +7735,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>666397</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Edouard Julien</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7798,26 +7798,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>39.3</v>
+        <v>51.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>55.7</v>
+        <v>39</v>
       </c>
       <c r="R27" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7884,127 +7884,127 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.1892</t>
+          <t>103.4467</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4604</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1666</t>
+          <t>0.2064</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3374</t>
+          <t>0.3351</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>75.08</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>53.08</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0886</t>
+          <t>0.1979</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.3632</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>68.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -10815,56 +10815,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>686469</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10882,22 +10882,22 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>39.8</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="n">
-        <v>36.9</v>
+        <v>48</v>
       </c>
       <c r="R38" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S38" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T38" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>16.6</v>
+        <v>30</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10949,12 +10949,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 4.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10979,102 +10979,102 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.2815</t>
+          <t>99.7536</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4109</t>
+          <t>0.4168</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3218</t>
+          <t>0.3228</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>73.32</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>13.66</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3954</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1416</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -11095,56 +11095,56 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>686469</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11162,22 +11162,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>36</v>
+        <v>39.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>36.9</v>
       </c>
       <c r="R39" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S39" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U39" t="n">
-        <v>25.8</v>
+        <v>16.6</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11259,102 +11259,102 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>99.7536</t>
+          <t>100.2815</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.4168</t>
+          <t>0.4109</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3228</t>
+          <t>0.3218</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>73.32</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.3954</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1416</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
         <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>44.8</v>
+        <v>43.2</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -12577,7 +12577,7 @@
         <v>80</v>
       </c>
       <c r="U44" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>50.3</v>
+        <v>47.7</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 6/19, 1 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -15015,56 +15015,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>608324</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15078,26 +15078,26 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>13.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>50.9</v>
+        <v>53.8</v>
       </c>
       <c r="R53" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S53" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
-        <v>91</v>
+        <v>25.3</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15149,27 +15149,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15179,112 +15179,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>96.2627</t>
+          <t>98.6862</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.3737</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.3195</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>68.76</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1385</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15295,27 +15295,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15325,26 +15325,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15358,26 +15358,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>32.9</v>
+        <v>13.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>36.3</v>
+        <v>50.9</v>
       </c>
       <c r="R54" t="n">
-        <v>68.3</v>
+        <v>55.6</v>
       </c>
       <c r="S54" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T54" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>34.9</v>
+        <v>91</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -15412,7 +15412,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -15429,27 +15429,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15459,112 +15459,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>98.9906</t>
+          <t>96.2627</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.3737</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.3032</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>68.76</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1637</t>
+          <t>0.1385</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15575,27 +15575,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15605,17 +15605,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15638,26 +15638,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>23.3</v>
+        <v>32.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>38.4</v>
+        <v>36.3</v>
       </c>
       <c r="R55" t="n">
-        <v>74.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="S55" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T55" t="n">
         <v>80</v>
       </c>
       <c r="U55" t="n">
-        <v>17</v>
+        <v>34.9</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15709,27 +15709,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15739,112 +15739,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>98.6007</t>
+          <t>98.9906</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3907</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.3405</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0968</t>
+          <t>0.1637</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15855,47 +15855,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>608324</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15918,26 +15918,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>26.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>53.8</v>
+        <v>38.4</v>
       </c>
       <c r="R56" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Last 7 games: 7/30, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -16019,112 +16019,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>98.6862</t>
+          <t>98.6007</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.3907</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3195</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.0968</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>37.01</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.54</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -18939,52 +18939,52 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>642201</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eli White</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -19002,26 +19002,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>25.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>50.9</v>
+        <v>37</v>
       </c>
       <c r="R67" t="n">
-        <v>55.6</v>
+        <v>52.7</v>
       </c>
       <c r="S67" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T67" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -19056,7 +19056,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -19073,27 +19073,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/5, 0 HR</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -19103,112 +19103,112 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>87.42</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>99.0505</t>
+          <t>100.9833</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.3792</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1241</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.2988</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>73.25</t>
+          <t>74.69</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.2737</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr"/>
@@ -19219,56 +19219,56 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>642201</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Eli White</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -19282,26 +19282,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>42.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q68" t="n">
-        <v>37</v>
+        <v>50.9</v>
       </c>
       <c r="R68" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S68" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T68" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U68" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19336,7 +19336,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -19353,27 +19353,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 0/5, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19383,112 +19383,112 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>87.42</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>100.9833</t>
+          <t>99.0505</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.3792</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1241</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.2838</t>
+          <t>0.2988</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>74.69</t>
+          <t>73.25</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.2737</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr"/>
@@ -19499,47 +19499,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>640902</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Jhonny Pereda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19562,26 +19562,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>36.8</v>
+        <v>28.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>53.8</v>
+        <v>38.4</v>
       </c>
       <c r="R69" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S69" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T69" t="n">
         <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>4.5</v>
+        <v>60.3</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19633,27 +19633,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19663,112 +19663,112 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>99.8545</t>
+          <t>100.6499</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.3825</t>
+          <t>0.4039</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3065</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.18</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
+          <t>0.1073</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>37.01</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>88.54</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>0.3774</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
           <t>0.1513</t>
         </is>
       </c>
-      <c r="BA69" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="BB69" t="inlineStr">
-        <is>
-          <t>42.07</t>
-        </is>
-      </c>
-      <c r="BC69" t="inlineStr">
-        <is>
-          <t>89.65</t>
-        </is>
-      </c>
-      <c r="BD69" t="inlineStr">
-        <is>
-          <t>0.4729</t>
-        </is>
-      </c>
-      <c r="BE69" t="inlineStr">
-        <is>
-          <t>0.2157</t>
-        </is>
-      </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19779,47 +19779,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>640902</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jhonny Pereda</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19842,26 +19842,26 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>28.3</v>
+        <v>9.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>38.4</v>
+        <v>54.4</v>
       </c>
       <c r="R70" t="n">
-        <v>74.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="S70" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U70" t="n">
-        <v>60.3</v>
+        <v>45.3</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19896,7 +19896,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19908,19 +19908,19 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="AJ70" t="inlineStr">
         <is>
           <t>1</t>
@@ -19928,127 +19928,127 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Last 3 games: 3/10, 1 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>100.6499</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4039</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20059,24 +20059,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>608348</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>2026-06-11T19:10:00Z</t>
@@ -20089,17 +20089,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>44.5</v>
+        <v>43.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20122,26 +20122,26 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>9.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>54.4</v>
+        <v>53.8</v>
       </c>
       <c r="R71" t="n">
         <v>57.2</v>
       </c>
       <c r="S71" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T71" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>45.3</v>
+        <v>36</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -20173,10 +20173,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20188,17 +20192,17 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -20208,112 +20212,112 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 3 games: 3/10, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>88.94</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>99.448</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.3182</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
@@ -20619,27 +20623,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>608348</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20649,17 +20653,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20668,7 +20672,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>43.7</v>
+        <v>42.7</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20686,22 +20690,22 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>29.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>53.8</v>
+        <v>48</v>
       </c>
       <c r="R73" t="n">
-        <v>57.2</v>
+        <v>52.7</v>
       </c>
       <c r="S73" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T73" t="n">
         <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20715,7 +20719,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20753,12 +20757,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -20768,12 +20772,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20783,112 +20787,112 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>88.94</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>99.448</t>
+          <t>98.04</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t>0.3028</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.3182</t>
+          <t>0.2913</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20899,47 +20903,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>690976</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Alex Freeland</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -20948,7 +20952,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20962,26 +20966,26 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>15.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="R74" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S74" t="n">
-        <v>86.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>32</v>
+        <v>23.7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20995,7 +20999,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -21038,7 +21042,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -21048,12 +21052,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Contact streak: 5/15 over last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -21063,102 +21067,102 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.9415</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.3028</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.2913</t>
+          <t>0.2915</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>70.63</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
@@ -21168,7 +21172,7 @@
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21179,47 +21183,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>690976</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -21228,7 +21232,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21246,22 +21250,22 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="R75" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S75" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T75" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>23.7</v>
+        <v>10.1</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21275,7 +21279,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21313,12 +21317,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21328,12 +21332,12 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21343,102 +21347,102 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>98.9415</t>
+          <t>98.8808</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2915</t>
+          <t>0.3017</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
@@ -21448,7 +21452,7 @@
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21459,47 +21463,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>806068</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Colt Emerson</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21508,7 +21512,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21522,26 +21526,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="Q76" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="R76" t="n">
-        <v>52.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S76" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T76" t="n">
         <v>80</v>
       </c>
       <c r="U76" t="n">
-        <v>12</v>
+        <v>56.2</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21555,7 +21559,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21576,7 +21580,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21593,27 +21597,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21623,112 +21627,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>98.8808</t>
+          <t>97.4401</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3017</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1485</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.01</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>88.54</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21739,47 +21743,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>806068</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Colt Emerson</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21788,7 +21792,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21802,26 +21806,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>15.7</v>
+        <v>21.3</v>
       </c>
       <c r="Q77" t="n">
-        <v>38.4</v>
+        <v>37</v>
       </c>
       <c r="R77" t="n">
-        <v>74.59999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="S77" t="n">
-        <v>44.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>56.2</v>
+        <v>25.8</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21835,7 +21839,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21856,7 +21860,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21873,7 +21877,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
@@ -21883,17 +21887,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21903,112 +21907,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>97.4401</t>
+          <t>99.3418</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.3552</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2946</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22019,27 +22023,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -22049,17 +22053,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22068,7 +22072,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22086,46 +22090,38 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="Q78" t="n">
-        <v>37</v>
+        <v>55.7</v>
       </c>
       <c r="R78" t="n">
-        <v>52.7</v>
+        <v>57.2</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T78" t="n">
         <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>27.7</v>
+        <v>21.5</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -22133,7 +22129,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22153,12 +22153,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22168,12 +22168,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22183,112 +22183,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.3418</t>
+          <t>99.3561</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.1054</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.2946</t>
+          <t>0.3105</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0895</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22299,27 +22299,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>670224</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Kameron Misner</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22329,17 +22329,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22348,7 +22348,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22362,57 +22362,61 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>55.7</v>
+        <v>48</v>
       </c>
       <c r="R79" t="n">
-        <v>57.2</v>
+        <v>52.7</v>
       </c>
       <c r="S79" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22424,17 +22428,17 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22444,12 +22448,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 2 games: 0/1, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22459,112 +22463,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>99.3561</t>
+          <t>98.4049</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1054</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3105</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0895</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22575,32 +22579,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>670224</t>
+          <t>700337</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kameron Misner</t>
+          <t>Edgar Quero</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -22610,17 +22614,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -22642,22 +22646,22 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>17.5</v>
+        <v>15.7</v>
       </c>
       <c r="Q80" t="n">
-        <v>48</v>
+        <v>44.4</v>
       </c>
       <c r="R80" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S80" t="n">
         <v>64.3</v>
       </c>
       <c r="T80" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22692,7 +22696,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22704,32 +22708,32 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/1, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22739,112 +22743,112 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>98.4049</t>
+          <t>98.5819</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2935</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.0848</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2634</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22855,56 +22859,56 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>700337</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Edgar Quero</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22922,22 +22926,22 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>15.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="R81" t="n">
-        <v>55.6</v>
+        <v>52.7</v>
       </c>
       <c r="S81" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T81" t="n">
         <v>75</v>
       </c>
       <c r="U81" t="n">
-        <v>28.9</v>
+        <v>19.5</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22951,7 +22955,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22989,27 +22993,27 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -23019,112 +23023,112 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>98.5819</t>
+          <t>99.6134</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.2935</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.0848</t>
+          <t>0.0962</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.2634</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>73.19</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.1095</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -23135,56 +23139,56 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23202,22 +23206,22 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>23.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q82" t="n">
-        <v>47.2</v>
+        <v>45.1</v>
       </c>
       <c r="R82" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S82" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T82" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U82" t="n">
-        <v>21.5</v>
+        <v>45</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -23231,7 +23235,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -23269,12 +23273,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23284,12 +23288,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Contact streak: 6/12 over last 7 games</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -23299,112 +23303,112 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>99.6134</t>
+          <t>99.7966</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3074</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.0962</t>
+          <t>0.0665</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2717</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1095</t>
+          <t>0.0239</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -23415,56 +23419,56 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -23478,26 +23482,26 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>14.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q83" t="n">
-        <v>45.1</v>
+        <v>53.8</v>
       </c>
       <c r="R83" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S83" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T83" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>45</v>
+        <v>10.8</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -23511,7 +23515,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -23549,12 +23553,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -23564,12 +23568,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Contact streak: 6/12 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -23579,112 +23583,112 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>99.7966</t>
+          <t>96.1991</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.3074</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.0665</t>
+          <t>0.0878</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.2717</t>
+          <t>0.3318</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>68.43</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.0239</t>
+          <t>0.0998</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23695,56 +23699,56 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23762,22 +23766,22 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>9.1</v>
+        <v>24.1</v>
       </c>
       <c r="Q84" t="n">
-        <v>53.8</v>
+        <v>45.1</v>
       </c>
       <c r="R84" t="n">
-        <v>57.2</v>
+        <v>55.6</v>
       </c>
       <c r="S84" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T84" t="n">
         <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -23791,7 +23795,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -23812,7 +23816,7 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -23829,12 +23833,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -23844,12 +23848,12 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23859,112 +23863,112 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>96.1991</t>
+          <t>98.0684</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.0878</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.3318</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.0998</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -24024,7 +24028,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -24057,7 +24061,7 @@
         <v>50</v>
       </c>
       <c r="U85" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -24114,7 +24118,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -24124,7 +24128,7 @@
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
@@ -24255,56 +24259,56 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>807713</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Matt Shaw</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -24322,46 +24326,38 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>24.1</v>
+        <v>17.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>45.1</v>
+        <v>53.8</v>
       </c>
       <c r="R86" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S86" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T86" t="n">
         <v>50</v>
       </c>
       <c r="U86" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -24369,10 +24365,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -24389,12 +24389,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24404,12 +24404,12 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 0/7, 0 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24419,112 +24419,112 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.81</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>98.0684</t>
+          <t>96.9848</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1317</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.2985</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1596</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>80</v>
       </c>
       <c r="U91" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
@@ -29061,47 +29061,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -29110,7 +29110,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -29124,26 +29124,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>65.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.3</v>
+        <v>53.3</v>
       </c>
       <c r="R12" t="n">
-        <v>68.3</v>
+        <v>57.2</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>54.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -29195,27 +29195,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -29225,112 +29225,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>102.3127</t>
+          <t>101.9188</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.5369</t>
+          <t>0.4577</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2716</t>
+          <t>0.2322</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3456</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2431</t>
+          <t>0.2351</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -29341,47 +29341,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -29390,7 +29390,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -29404,26 +29404,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.2</v>
+        <v>65.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="R13" t="n">
-        <v>57.2</v>
+        <v>68.3</v>
       </c>
       <c r="S13" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -29475,27 +29475,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -29505,112 +29505,112 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.9188</t>
+          <t>102.3127</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4577</t>
+          <t>0.5369</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2322</t>
+          <t>0.2716</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3456</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.2351</t>
+          <t>0.2431</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -31021,47 +31021,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -31088,22 +31088,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>49.4</v>
+        <v>53.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.3</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S19" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>53.9</v>
+        <v>28.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -31155,12 +31155,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -31170,12 +31170,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -31195,92 +31195,92 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.0569</t>
+          <t>102.7456</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4887</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2126</t>
+          <t>0.1927</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3675</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -31301,47 +31301,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -31350,7 +31350,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -31368,22 +31368,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>36.3</v>
       </c>
       <c r="R20" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S20" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>23.4</v>
+        <v>53.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -31435,12 +31435,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -31450,12 +31450,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -31475,92 +31475,92 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7456</t>
+          <t>101.0569</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4887</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1927</t>
+          <t>0.2126</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -31663,7 +31663,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
